--- a/outputs/8942.xlsx
+++ b/outputs/8942.xlsx
@@ -152,40 +152,44 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -441,117 +445,117 @@
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>42398</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="4" t="n">
         <f aca="false">INDEX('Pay Dates'!$B:$B,MATCH(Overview!$A2,'Pay Dates'!$A:$A,0))</f>
         <v>1000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <f aca="false">INDEX('Pay Dates'!$C:$C,MATCH(Overview!$A2,'Pay Dates'!$A:$A,0))</f>
         <v>1000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
+      <c r="A3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <f aca="false">SUM(B2:C2)</f>
         <v>2000</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="n">
-        <f aca="false">SUMIFS('Pay Dates'!$B:$B,'Pay Dates'!$A:$A,"&gt;="&amp;EOMONTH(Overview!$A2,-1)+1,'Pay Dates'!$A:$A,"&lt;="&amp;EOMONTH(Overview!$A2,0))+SUMIFS('Pay Dates'!$C:$C,'Pay Dates'!$A:$A,"&gt;="&amp;EOMONTH(Overview!$A2,-1)+1,'Pay Dates'!$A:$A,"&lt;="&amp;EOMONTH(Overview!$A2,0))</f>
+      <c r="B5" s="6" t="n">
+        <f aca="false">SUMPRODUCT(('Pay Dates'!$A$2:$A$27&gt;=DATE(YEAR(Overview!$A2),MONTH(Overview!$A2),1))*('Pay Dates'!$A$2:$A$27&lt;=EOMONTH(Overview!$A2,0))*('Pay Dates'!B2:B27+'Pay Dates'!C2:C27))</f>
         <v>4800</v>
       </c>
-      <c r="C5" s="5"/>
+      <c r="C5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7"/>
+      <c r="A6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7"/>
+      <c r="A7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7"/>
+      <c r="A8" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7"/>
+      <c r="A11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7"/>
+      <c r="A12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7"/>
+      <c r="A13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7"/>
+      <c r="A14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
+      <c r="A15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
+      <c r="A16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
+      <c r="A17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
+      <c r="A18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
+      <c r="A19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
+      <c r="A20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7"/>
+      <c r="A21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7"/>
+      <c r="A22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7"/>
+      <c r="A23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7"/>
+      <c r="A24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7"/>
+      <c r="A25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7"/>
+      <c r="A26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7"/>
+      <c r="A27" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -577,299 +581,299 @@
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="n">
+      <c r="A2" s="9" t="n">
         <v>42370</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="9" t="n">
         <v>42384</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="9" t="n">
         <v>42398</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C4" s="0" t="n">
+      <c r="B4" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="9" t="n">
         <v>42412</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="9" t="n">
         <v>42426</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="9" t="n">
         <v>42440</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="9" t="n">
         <v>42454</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="9" t="n">
         <v>42468</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="9" t="n">
         <v>42482</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C10" s="0" t="n">
+      <c r="B10" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="9" t="n">
         <v>42496</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="9" t="n">
         <v>42510</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="9" t="n">
         <v>42524</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="9" t="n">
         <v>42538</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="1" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="9" t="n">
         <v>42552</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="9" t="n">
         <v>42566</v>
       </c>
-      <c r="B16" s="0" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C16" s="0" t="n">
+      <c r="B16" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C16" s="1" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="9" t="n">
         <v>42580</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="9" t="n">
         <v>42594</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="1" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="9" t="n">
         <v>42608</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="1" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="9" t="n">
         <v>42622</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="1" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="9" t="n">
         <v>42636</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21" s="1" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="9" t="n">
         <v>42650</v>
       </c>
-      <c r="B22" s="0" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C22" s="0" t="n">
+      <c r="B22" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C22" s="1" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="9" t="n">
         <v>42678</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="1" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="9" t="n">
         <v>42692</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="1" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="9" t="n">
         <v>42706</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25" s="1" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="9" t="n">
         <v>42720</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26" s="1" t="n">
         <v>900</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="9" t="n">
         <v>42734</v>
       </c>
-      <c r="B27" s="0" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C27" s="0" t="n">
+      <c r="B27" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C27" s="1" t="n">
         <v>5000</v>
       </c>
     </row>

--- a/outputs/8942.xlsx
+++ b/outputs/8942.xlsx
@@ -492,7 +492,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">SUMPRODUCT(('Pay Dates'!$A$2:$A$27&gt;=DATE(YEAR(Overview!$A2),MONTH(Overview!$A2),1))*('Pay Dates'!$A$2:$A$27&lt;=EOMONTH(Overview!$A2,0))*('Pay Dates'!B2:B27+'Pay Dates'!C2:C27))</f>
+        <f aca="false">SUMPRODUCT((MONTH('Pay Dates'!$A$2:$A$27)=MONTH(Overview!$A2))*('Pay Dates'!$B$2:$B$27+ 'Pay Dates'!$C$2:$C$27))</f>
         <v>4800</v>
       </c>
       <c r="C5" s="6"/>
